--- a/results.xlsx
+++ b/results.xlsx
@@ -8,21 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Turan\Desktop\PwC-x-TUM-RL-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13096424-6BB4-47A6-B83F-526A486D392E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19CB98F-0E52-4832-976A-98EF7A96A897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Historical" sheetId="2" r:id="rId2"/>
-    <sheet name="Future Projection" sheetId="3" r:id="rId3"/>
+    <sheet name="Policy Comparison" sheetId="2" r:id="rId2"/>
+    <sheet name="Historical (PPO)" sheetId="3" r:id="rId3"/>
+    <sheet name="Future Projection" sheetId="4" r:id="rId4"/>
+    <sheet name="BS S=80" sheetId="5" r:id="rId5"/>
+    <sheet name="BS S=120" sheetId="6" r:id="rId6"/>
+    <sheet name="BS S=160" sheetId="7" r:id="rId7"/>
+    <sheet name="BS S=200" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="132">
   <si>
     <t>Metric</t>
   </si>
@@ -58,6 +63,33 @@
   </si>
   <si>
     <t>Projected Weeks</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>Total Ordered</t>
+  </si>
+  <si>
+    <t>Avg Inventory</t>
+  </si>
+  <si>
+    <t>Lost Sales (units)</t>
+  </si>
+  <si>
+    <t>PPO Agent</t>
+  </si>
+  <si>
+    <t>Base Stock S=80</t>
+  </si>
+  <si>
+    <t>Base Stock S=120</t>
+  </si>
+  <si>
+    <t>Base Stock S=160</t>
+  </si>
+  <si>
+    <t>Base Stock S=200</t>
   </si>
   <si>
     <t>Week</t>
@@ -766,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>158845</v>
+        <v>126051</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +814,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>1393</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>168.91</v>
+        <v>99.59</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -816,6 +848,144 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>126051</v>
+      </c>
+      <c r="C2">
+        <v>99.840637450199196</v>
+      </c>
+      <c r="D2">
+        <v>1327</v>
+      </c>
+      <c r="E2">
+        <v>99.59375</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>265950</v>
+      </c>
+      <c r="C3">
+        <v>93.864541832669318</v>
+      </c>
+      <c r="D3">
+        <v>1170</v>
+      </c>
+      <c r="E3">
+        <v>7.8125</v>
+      </c>
+      <c r="F3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>99130</v>
+      </c>
+      <c r="C4">
+        <v>99.840637450199196</v>
+      </c>
+      <c r="D4">
+        <v>1285</v>
+      </c>
+      <c r="E4">
+        <v>40.9375</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>117130</v>
+      </c>
+      <c r="C5">
+        <v>99.840637450199196</v>
+      </c>
+      <c r="D5">
+        <v>1325</v>
+      </c>
+      <c r="E5">
+        <v>78.4375</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>135130</v>
+      </c>
+      <c r="C6">
+        <v>99.840637450199196</v>
+      </c>
+      <c r="D6">
+        <v>1365</v>
+      </c>
+      <c r="E6">
+        <v>115.9375</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -834,34 +1004,34 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K1" t="s">
         <v>6</v>
@@ -869,10 +1039,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>46</v>
@@ -881,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -893,21 +1063,21 @@
         <v>546</v>
       </c>
       <c r="I2">
-        <v>10500</v>
+        <v>8160</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11046</v>
+        <v>8706</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>44</v>
@@ -916,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -928,517 +1098,517 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>6540</v>
+        <v>1620</v>
       </c>
       <c r="J3">
         <v>5000</v>
       </c>
       <c r="K3">
-        <v>11540</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C4">
         <v>39</v>
       </c>
       <c r="D4">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="H4">
-        <v>1768</v>
+        <v>1261</v>
       </c>
       <c r="I4">
-        <v>960</v>
+        <v>3300</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2728</v>
+        <v>4561</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5">
         <v>56</v>
       </c>
       <c r="D5">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="H5">
-        <v>2457</v>
+        <v>884</v>
       </c>
       <c r="I5">
-        <v>3180</v>
+        <v>4140</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>5637</v>
+        <v>5024</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E6">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>174</v>
+        <v>92</v>
       </c>
       <c r="H6">
-        <v>2262</v>
+        <v>1196</v>
       </c>
       <c r="I6">
-        <v>6180</v>
+        <v>3780</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>8442</v>
+        <v>4976</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
       <c r="D7">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="H7">
-        <v>2535</v>
+        <v>1677</v>
       </c>
       <c r="I7">
-        <v>2700</v>
+        <v>1620</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5235</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>47</v>
       </c>
       <c r="D8">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>251</v>
+        <v>145</v>
       </c>
       <c r="H8">
-        <v>3263</v>
+        <v>1885</v>
       </c>
       <c r="I8">
-        <v>240</v>
+        <v>2700</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3503</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>48</v>
       </c>
       <c r="D9">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>248</v>
+        <v>124</v>
       </c>
       <c r="H9">
-        <v>3224</v>
+        <v>1612</v>
       </c>
       <c r="I9">
-        <v>900</v>
+        <v>2280</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>4124</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>30</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="H10">
-        <v>2886</v>
+        <v>1807</v>
       </c>
       <c r="I10">
-        <v>2400</v>
+        <v>1920</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>5286</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>41</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E11">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="H11">
-        <v>2548</v>
+        <v>1768</v>
       </c>
       <c r="I11">
-        <v>2580</v>
+        <v>2100</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>5128</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>43</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>193</v>
+        <v>125</v>
       </c>
       <c r="H12">
-        <v>2509</v>
+        <v>1625</v>
       </c>
       <c r="I12">
-        <v>1800</v>
+        <v>1980</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>4309</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C13">
         <v>34</v>
       </c>
       <c r="D13">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>202</v>
+        <v>126</v>
       </c>
       <c r="H13">
-        <v>2626</v>
+        <v>1638</v>
       </c>
       <c r="I13">
-        <v>1860</v>
+        <v>2400</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>4486</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>34</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E14">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="H14">
-        <v>2574</v>
+        <v>1625</v>
       </c>
       <c r="I14">
-        <v>2460</v>
+        <v>2160</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>5034</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C15">
         <v>26</v>
       </c>
       <c r="D15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="H15">
-        <v>2639</v>
+        <v>1807</v>
       </c>
       <c r="I15">
-        <v>2820</v>
+        <v>2400</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>5459</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C16">
         <v>44</v>
       </c>
       <c r="D16">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E16">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>200</v>
+        <v>131</v>
       </c>
       <c r="H16">
-        <v>2600</v>
+        <v>1703</v>
       </c>
       <c r="I16">
-        <v>2040</v>
+        <v>1860</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>4640</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <v>32</v>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E17">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>215</v>
+        <v>139</v>
       </c>
       <c r="H17">
-        <v>2795</v>
+        <v>1807</v>
       </c>
       <c r="I17">
-        <v>1980</v>
+        <v>2460</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>4775</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>50</v>
       </c>
       <c r="D18">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E18">
         <v>29</v>
@@ -1447,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>199</v>
+        <v>120</v>
       </c>
       <c r="H18">
-        <v>2587</v>
+        <v>1560</v>
       </c>
       <c r="I18">
         <v>1740</v>
@@ -1459,50 +1629,50 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>4327</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C19">
         <v>44</v>
       </c>
       <c r="D19">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E19">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="H19">
-        <v>2444</v>
+        <v>1521</v>
       </c>
       <c r="I19">
-        <v>2400</v>
+        <v>2580</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>4844</v>
+        <v>4101</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C20">
         <v>47</v>
@@ -1511,480 +1681,480 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="H20">
-        <v>2210</v>
+        <v>1287</v>
       </c>
       <c r="I20">
-        <v>2460</v>
+        <v>1920</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>4670</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C21">
         <v>33</v>
       </c>
       <c r="D21">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="H21">
-        <v>2301</v>
+        <v>1417</v>
       </c>
       <c r="I21">
-        <v>2160</v>
+        <v>2340</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>4461</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C22">
         <v>39</v>
       </c>
       <c r="D22">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="H22">
-        <v>2327</v>
+        <v>1326</v>
       </c>
       <c r="I22">
-        <v>1260</v>
+        <v>1620</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>3587</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C23">
         <v>43</v>
       </c>
       <c r="D23">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="H23">
-        <v>2236</v>
+        <v>1274</v>
       </c>
       <c r="I23">
-        <v>1260</v>
+        <v>1800</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>3496</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C24">
         <v>32</v>
       </c>
       <c r="D24">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="H24">
-        <v>2093</v>
+        <v>1209</v>
       </c>
       <c r="I24">
-        <v>2520</v>
+        <v>2400</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>4613</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C25">
         <v>51</v>
       </c>
       <c r="D25">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E25">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="H25">
-        <v>1703</v>
+        <v>936</v>
       </c>
       <c r="I25">
-        <v>2460</v>
+        <v>1800</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4163</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <v>43</v>
       </c>
       <c r="D26">
+        <v>40</v>
+      </c>
+      <c r="E26">
         <v>42</v>
       </c>
-      <c r="E26">
-        <v>39</v>
-      </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="H26">
-        <v>1690</v>
+        <v>897</v>
       </c>
       <c r="I26">
-        <v>2340</v>
+        <v>2520</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>4030</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>42</v>
       </c>
       <c r="D27">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="H27">
-        <v>1677</v>
+        <v>741</v>
       </c>
       <c r="I27">
-        <v>2460</v>
+        <v>2520</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>4137</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C28">
         <v>31</v>
       </c>
       <c r="D28">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E28">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="H28">
-        <v>1781</v>
+        <v>884</v>
       </c>
       <c r="I28">
-        <v>2280</v>
+        <v>1920</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>4061</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C29">
         <v>28</v>
       </c>
       <c r="D29">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="H29">
-        <v>1950</v>
+        <v>1066</v>
       </c>
       <c r="I29">
-        <v>1980</v>
+        <v>2400</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>3930</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C30">
         <v>24</v>
       </c>
       <c r="D30">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="H30">
-        <v>2132</v>
+        <v>1170</v>
       </c>
       <c r="I30">
-        <v>1980</v>
+        <v>2040</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>4112</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C31">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="H31">
-        <v>2171</v>
+        <v>1300</v>
       </c>
       <c r="I31">
-        <v>1740</v>
+        <v>1680</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>3911</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C32">
         <v>51</v>
       </c>
       <c r="D32">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F32">
         <v>0</v>
       </c>
       <c r="G32">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="H32">
-        <v>1937</v>
+        <v>1079</v>
       </c>
       <c r="I32">
-        <v>1980</v>
+        <v>2280</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>3917</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C33">
         <v>40</v>
       </c>
       <c r="D33">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E33">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F33">
         <v>0</v>
       </c>
       <c r="G33">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="H33">
-        <v>1794</v>
+        <v>923</v>
       </c>
       <c r="I33">
-        <v>3420</v>
+        <v>3180</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>5214</v>
+        <v>4103</v>
       </c>
     </row>
   </sheetData>
@@ -1992,8 +2162,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2011,31 +2181,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
         <v>6</v>
@@ -2043,121 +2213,121 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C2">
         <v>42</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="F2">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>1677</v>
+        <v>871</v>
       </c>
       <c r="H2">
-        <v>4980</v>
+        <v>3360</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>6657</v>
+        <v>4231</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>43</v>
       </c>
       <c r="D3">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F3">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="G3">
-        <v>1859</v>
+        <v>1001</v>
       </c>
       <c r="H3">
-        <v>3480</v>
+        <v>3300</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>5339</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>42</v>
       </c>
       <c r="D4">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E4">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="G4">
-        <v>2392</v>
+        <v>1183</v>
       </c>
       <c r="H4">
-        <v>2460</v>
+        <v>3000</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>4852</v>
+        <v>4183</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>34</v>
       </c>
       <c r="D5">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E5">
         <v>54</v>
       </c>
       <c r="F5">
-        <v>208</v>
+        <v>112</v>
       </c>
       <c r="G5">
-        <v>2704</v>
+        <v>1456</v>
       </c>
       <c r="H5">
         <v>3240</v>
@@ -2166,47 +2336,47 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>5944</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>54</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F6">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="G6">
-        <v>2535</v>
+        <v>1404</v>
       </c>
       <c r="H6">
-        <v>3720</v>
+        <v>3240</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>6255</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C7">
         <v>54</v>
@@ -2215,397 +2385,397 @@
         <v>54</v>
       </c>
       <c r="E7">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="G7">
-        <v>2535</v>
+        <v>1404</v>
       </c>
       <c r="H7">
-        <v>2760</v>
+        <v>2340</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>5295</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>54</v>
       </c>
       <c r="D8">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E8">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F8">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="G8">
-        <v>2639</v>
+        <v>1404</v>
       </c>
       <c r="H8">
-        <v>2340</v>
+        <v>3300</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>4979</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C9">
         <v>54</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E9">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9">
-        <v>195</v>
+        <v>93</v>
       </c>
       <c r="G9">
-        <v>2535</v>
+        <v>1209</v>
       </c>
       <c r="H9">
-        <v>2460</v>
+        <v>2640</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>4995</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10">
         <v>37</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E10">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="G10">
-        <v>2561</v>
+        <v>1443</v>
       </c>
       <c r="H10">
-        <v>2460</v>
+        <v>2280</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>5021</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C11">
         <v>46</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="G11">
-        <v>2496</v>
+        <v>1417</v>
       </c>
       <c r="H11">
-        <v>2280</v>
+        <v>2640</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>4776</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C12">
         <v>46</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F12">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="G12">
-        <v>2431</v>
+        <v>1313</v>
       </c>
       <c r="H12">
-        <v>2040</v>
+        <v>2280</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>4471</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C13">
         <v>37</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F13">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="G13">
-        <v>2444</v>
+        <v>1404</v>
       </c>
       <c r="H13">
-        <v>2340</v>
+        <v>2640</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>4784</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>36</v>
       </c>
       <c r="D14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F14">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="G14">
-        <v>2418</v>
+        <v>1430</v>
       </c>
       <c r="H14">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>5118</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C15">
         <v>36</v>
       </c>
       <c r="D15">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E15">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F15">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="G15">
-        <v>2457</v>
+        <v>1534</v>
       </c>
       <c r="H15">
-        <v>2820</v>
+        <v>2580</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>5277</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>44</v>
       </c>
       <c r="D16">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F16">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="G16">
-        <v>2470</v>
+        <v>1482</v>
       </c>
       <c r="H16">
-        <v>2520</v>
+        <v>2400</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>4990</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C17">
         <v>44</v>
       </c>
       <c r="D17">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E17">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="G17">
-        <v>2509</v>
+        <v>1469</v>
       </c>
       <c r="H17">
-        <v>2220</v>
+        <v>2460</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>4729</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C18">
         <v>44</v>
       </c>
       <c r="D18">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E18">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="G18">
-        <v>2483</v>
+        <v>1417</v>
       </c>
       <c r="H18">
-        <v>2220</v>
+        <v>2400</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>4703</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C19">
         <v>39</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E19">
         <v>39</v>
       </c>
       <c r="F19">
-        <v>189</v>
+        <v>111</v>
       </c>
       <c r="G19">
-        <v>2457</v>
+        <v>1443</v>
       </c>
       <c r="H19">
         <v>2340</v>
@@ -2614,47 +2784,47 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>4797</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C20">
         <v>39</v>
       </c>
       <c r="D20">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="G20">
-        <v>2431</v>
+        <v>1456</v>
       </c>
       <c r="H20">
-        <v>1980</v>
+        <v>1860</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>4411</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>39</v>
@@ -2663,141 +2833,141 @@
         <v>39</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="G21">
-        <v>2431</v>
+        <v>1456</v>
       </c>
       <c r="H21">
-        <v>1620</v>
+        <v>2100</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>4051</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C22">
         <v>39</v>
       </c>
       <c r="D22">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="G22">
-        <v>2353</v>
+        <v>1352</v>
       </c>
       <c r="H22">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3853</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C23">
         <v>28</v>
       </c>
       <c r="D23">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="G23">
-        <v>2340</v>
+        <v>1443</v>
       </c>
       <c r="H23">
-        <v>1620</v>
+        <v>1740</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>3960</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C24">
         <v>28</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E24">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="G24">
-        <v>2301</v>
+        <v>1469</v>
       </c>
       <c r="H24">
-        <v>1740</v>
+        <v>1800</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>4041</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C25">
         <v>28</v>
       </c>
       <c r="D25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E25">
         <v>28</v>
       </c>
       <c r="F25">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="G25">
-        <v>2288</v>
+        <v>1482</v>
       </c>
       <c r="H25">
         <v>1680</v>
@@ -2806,47 +2976,47 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>3968</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C26">
         <v>28</v>
       </c>
       <c r="D26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="G26">
-        <v>2301</v>
+        <v>1508</v>
       </c>
       <c r="H26">
-        <v>1440</v>
+        <v>1500</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>3741</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>28</v>
@@ -2855,141 +3025,2243 @@
         <v>28</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F27">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="G27">
-        <v>2301</v>
+        <v>1508</v>
       </c>
       <c r="H27">
-        <v>1560</v>
+        <v>1800</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>3861</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C28">
         <v>28</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F28">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="G28">
-        <v>2249</v>
+        <v>1469</v>
       </c>
       <c r="H28">
-        <v>1440</v>
+        <v>1320</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>3689</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>23</v>
       </c>
       <c r="D29">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E29">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F29">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="G29">
-        <v>2288</v>
+        <v>1560</v>
       </c>
       <c r="H29">
-        <v>1620</v>
+        <v>1860</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>3908</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>28</v>
       </c>
       <c r="D30">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F30">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="G30">
-        <v>2236</v>
+        <v>1482</v>
       </c>
       <c r="H30">
-        <v>1740</v>
+        <v>1560</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>3976</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C31">
         <v>23</v>
       </c>
       <c r="D31">
+        <v>31</v>
+      </c>
+      <c r="E31">
+        <v>28</v>
+      </c>
+      <c r="F31">
+        <v>122</v>
+      </c>
+      <c r="G31">
+        <v>1586</v>
+      </c>
+      <c r="H31">
+        <v>1680</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>119</v>
+      </c>
+      <c r="G32">
+        <v>1547</v>
+      </c>
+      <c r="H32">
+        <v>1740</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>28</v>
+      </c>
+      <c r="E33">
+        <v>38</v>
+      </c>
+      <c r="F33">
+        <v>118</v>
+      </c>
+      <c r="G33">
+        <v>1534</v>
+      </c>
+      <c r="H33">
+        <v>2280</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>29</v>
+      </c>
+      <c r="E34">
+        <v>33</v>
+      </c>
+      <c r="F34">
+        <v>118</v>
+      </c>
+      <c r="G34">
+        <v>1534</v>
+      </c>
+      <c r="H34">
+        <v>1980</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>3514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35">
+        <v>29</v>
+      </c>
+      <c r="D35">
+        <v>38</v>
+      </c>
+      <c r="E35">
+        <v>38</v>
+      </c>
+      <c r="F35">
+        <v>127</v>
+      </c>
+      <c r="G35">
+        <v>1651</v>
+      </c>
+      <c r="H35">
+        <v>2280</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36">
+        <v>40</v>
+      </c>
+      <c r="D36">
+        <v>33</v>
+      </c>
+      <c r="E36">
+        <v>38</v>
+      </c>
+      <c r="F36">
+        <v>120</v>
+      </c>
+      <c r="G36">
+        <v>1560</v>
+      </c>
+      <c r="H36">
+        <v>2280</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37">
+        <v>40</v>
+      </c>
+      <c r="D37">
+        <v>38</v>
+      </c>
+      <c r="E37">
+        <v>36</v>
+      </c>
+      <c r="F37">
+        <v>118</v>
+      </c>
+      <c r="G37">
+        <v>1534</v>
+      </c>
+      <c r="H37">
+        <v>2160</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38">
+        <v>40</v>
+      </c>
+      <c r="D38">
+        <v>38</v>
+      </c>
+      <c r="E38">
+        <v>38</v>
+      </c>
+      <c r="F38">
+        <v>116</v>
+      </c>
+      <c r="G38">
+        <v>1508</v>
+      </c>
+      <c r="H38">
+        <v>2280</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39">
+        <v>40</v>
+      </c>
+      <c r="D39">
+        <v>36</v>
+      </c>
+      <c r="E39">
+        <v>36</v>
+      </c>
+      <c r="F39">
+        <v>112</v>
+      </c>
+      <c r="G39">
+        <v>1456</v>
+      </c>
+      <c r="H39">
+        <v>2160</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40">
+        <v>37</v>
+      </c>
+      <c r="D40">
+        <v>38</v>
+      </c>
+      <c r="E40">
+        <v>37</v>
+      </c>
+      <c r="F40">
+        <v>113</v>
+      </c>
+      <c r="G40">
+        <v>1469</v>
+      </c>
+      <c r="H40">
+        <v>2220</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41">
+        <v>36</v>
+      </c>
+      <c r="D41">
+        <v>36</v>
+      </c>
+      <c r="E41">
+        <v>37</v>
+      </c>
+      <c r="F41">
+        <v>113</v>
+      </c>
+      <c r="G41">
+        <v>1469</v>
+      </c>
+      <c r="H41">
+        <v>2220</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42">
+        <v>36</v>
+      </c>
+      <c r="D42">
+        <v>37</v>
+      </c>
+      <c r="E42">
+        <v>38</v>
+      </c>
+      <c r="F42">
+        <v>114</v>
+      </c>
+      <c r="G42">
+        <v>1482</v>
+      </c>
+      <c r="H42">
+        <v>2280</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43">
+        <v>36</v>
+      </c>
+      <c r="D43">
+        <v>37</v>
+      </c>
+      <c r="E43">
+        <v>32</v>
+      </c>
+      <c r="F43">
+        <v>115</v>
+      </c>
+      <c r="G43">
+        <v>1495</v>
+      </c>
+      <c r="H43">
+        <v>1920</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44">
+        <v>37</v>
+      </c>
+      <c r="D44">
+        <v>38</v>
+      </c>
+      <c r="E44">
+        <v>42</v>
+      </c>
+      <c r="F44">
+        <v>116</v>
+      </c>
+      <c r="G44">
+        <v>1508</v>
+      </c>
+      <c r="H44">
+        <v>2520</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45">
+        <v>39</v>
+      </c>
+      <c r="D45">
+        <v>32</v>
+      </c>
+      <c r="E45">
+        <v>35</v>
+      </c>
+      <c r="F45">
+        <v>109</v>
+      </c>
+      <c r="G45">
+        <v>1417</v>
+      </c>
+      <c r="H45">
+        <v>2100</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>3517</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46">
+        <v>32</v>
+      </c>
+      <c r="D46">
+        <v>42</v>
+      </c>
+      <c r="E46">
+        <v>44</v>
+      </c>
+      <c r="F46">
+        <v>119</v>
+      </c>
+      <c r="G46">
+        <v>1547</v>
+      </c>
+      <c r="H46">
+        <v>2640</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+      <c r="B47" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47">
+        <v>39</v>
+      </c>
+      <c r="D47">
+        <v>35</v>
+      </c>
+      <c r="E47">
+        <v>41</v>
+      </c>
+      <c r="F47">
+        <v>115</v>
+      </c>
+      <c r="G47">
+        <v>1495</v>
+      </c>
+      <c r="H47">
+        <v>2460</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48">
+        <v>39</v>
+      </c>
+      <c r="D48">
+        <v>44</v>
+      </c>
+      <c r="E48">
+        <v>43</v>
+      </c>
+      <c r="F48">
+        <v>120</v>
+      </c>
+      <c r="G48">
+        <v>1560</v>
+      </c>
+      <c r="H48">
+        <v>2580</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49">
+        <v>45</v>
+      </c>
+      <c r="D49">
+        <v>41</v>
+      </c>
+      <c r="E49">
+        <v>44</v>
+      </c>
+      <c r="F49">
+        <v>116</v>
+      </c>
+      <c r="G49">
+        <v>1508</v>
+      </c>
+      <c r="H49">
+        <v>2640</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50">
+        <v>45</v>
+      </c>
+      <c r="D50">
+        <v>43</v>
+      </c>
+      <c r="E50">
+        <v>34</v>
+      </c>
+      <c r="F50">
+        <v>114</v>
+      </c>
+      <c r="G50">
+        <v>1482</v>
+      </c>
+      <c r="H50">
+        <v>2040</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+      <c r="B51" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51">
+        <v>45</v>
+      </c>
+      <c r="D51">
+        <v>44</v>
+      </c>
+      <c r="E51">
+        <v>33</v>
+      </c>
+      <c r="F51">
+        <v>113</v>
+      </c>
+      <c r="G51">
+        <v>1469</v>
+      </c>
+      <c r="H51">
+        <v>1980</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3449</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52">
+        <v>45</v>
+      </c>
+      <c r="D52">
+        <v>34</v>
+      </c>
+      <c r="E52">
+        <v>31</v>
+      </c>
+      <c r="F52">
+        <v>102</v>
+      </c>
+      <c r="G52">
+        <v>1326</v>
+      </c>
+      <c r="H52">
+        <v>1860</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53">
+        <v>33</v>
+      </c>
+      <c r="D53">
+        <v>33</v>
+      </c>
+      <c r="E53">
         <v>27</v>
       </c>
+      <c r="F53">
+        <v>102</v>
+      </c>
+      <c r="G53">
+        <v>1326</v>
+      </c>
+      <c r="H53">
+        <v>1620</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54">
+        <v>24</v>
+      </c>
+      <c r="D54">
+        <v>31</v>
+      </c>
+      <c r="E54">
+        <v>26</v>
+      </c>
+      <c r="F54">
+        <v>109</v>
+      </c>
+      <c r="G54">
+        <v>1417</v>
+      </c>
+      <c r="H54">
+        <v>1560</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55">
+        <v>24</v>
+      </c>
+      <c r="D55">
+        <v>27</v>
+      </c>
+      <c r="E55">
+        <v>48</v>
+      </c>
+      <c r="F55">
+        <v>112</v>
+      </c>
+      <c r="G55">
+        <v>1456</v>
+      </c>
+      <c r="H55">
+        <v>2880</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56">
+        <v>24</v>
+      </c>
+      <c r="D56">
+        <v>26</v>
+      </c>
+      <c r="E56">
+        <v>34</v>
+      </c>
+      <c r="F56">
+        <v>114</v>
+      </c>
+      <c r="G56">
+        <v>1482</v>
+      </c>
+      <c r="H56">
+        <v>2040</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>3522</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57">
+        <v>24</v>
+      </c>
+      <c r="D57">
+        <v>48</v>
+      </c>
+      <c r="E57">
+        <v>47</v>
+      </c>
+      <c r="F57">
+        <v>138</v>
+      </c>
+      <c r="G57">
+        <v>1794</v>
+      </c>
+      <c r="H57">
+        <v>2820</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58">
+        <v>50</v>
+      </c>
+      <c r="D58">
+        <v>34</v>
+      </c>
+      <c r="E58">
+        <v>45</v>
+      </c>
+      <c r="F58">
+        <v>122</v>
+      </c>
+      <c r="G58">
+        <v>1586</v>
+      </c>
+      <c r="H58">
+        <v>2700</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59">
+        <v>50</v>
+      </c>
+      <c r="D59">
+        <v>47</v>
+      </c>
+      <c r="E59">
+        <v>43</v>
+      </c>
+      <c r="F59">
+        <v>119</v>
+      </c>
+      <c r="G59">
+        <v>1547</v>
+      </c>
+      <c r="H59">
+        <v>2580</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60">
+        <v>50</v>
+      </c>
+      <c r="D60">
+        <v>45</v>
+      </c>
+      <c r="E60">
+        <v>33</v>
+      </c>
+      <c r="F60">
+        <v>114</v>
+      </c>
+      <c r="G60">
+        <v>1482</v>
+      </c>
+      <c r="H60">
+        <v>1980</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>3462</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>127</v>
+      </c>
+      <c r="B61" t="s">
+        <v>125</v>
+      </c>
+      <c r="C61">
+        <v>50</v>
+      </c>
+      <c r="D61">
+        <v>43</v>
+      </c>
+      <c r="E61">
+        <v>53</v>
+      </c>
+      <c r="F61">
+        <v>107</v>
+      </c>
+      <c r="G61">
+        <v>1391</v>
+      </c>
+      <c r="H61">
+        <v>3180</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62">
+        <v>44</v>
+      </c>
+      <c r="D62">
+        <v>33</v>
+      </c>
+      <c r="E62">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>96</v>
+      </c>
+      <c r="G62">
+        <v>1248</v>
+      </c>
+      <c r="H62">
+        <v>1740</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2988</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63">
+        <v>27</v>
+      </c>
+      <c r="D63">
+        <v>53</v>
+      </c>
+      <c r="E63">
+        <v>41</v>
+      </c>
+      <c r="F63">
+        <v>122</v>
+      </c>
+      <c r="G63">
+        <v>1586</v>
+      </c>
+      <c r="H63">
+        <v>2460</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" t="s">
+        <v>128</v>
+      </c>
+      <c r="C64">
+        <v>45</v>
+      </c>
+      <c r="D64">
+        <v>29</v>
+      </c>
+      <c r="E64">
+        <v>38</v>
+      </c>
+      <c r="F64">
+        <v>106</v>
+      </c>
+      <c r="G64">
+        <v>1378</v>
+      </c>
+      <c r="H64">
+        <v>2280</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65">
+        <v>36</v>
+      </c>
+      <c r="D65">
+        <v>41</v>
+      </c>
+      <c r="E65">
+        <v>36</v>
+      </c>
+      <c r="F65">
+        <v>111</v>
+      </c>
+      <c r="G65">
+        <v>1443</v>
+      </c>
+      <c r="H65">
+        <v>2160</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>3603</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>38</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>546</v>
+      </c>
+      <c r="H2">
+        <v>2280</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2520</v>
+      </c>
+      <c r="I3">
+        <v>5000</v>
+      </c>
+      <c r="J3">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>38</v>
+      </c>
+      <c r="D4">
+        <v>38</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>2280</v>
+      </c>
+      <c r="I4">
+        <v>2500</v>
+      </c>
+      <c r="J4">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>42</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>2520</v>
+      </c>
+      <c r="I5">
+        <v>35000</v>
+      </c>
+      <c r="J5">
+        <v>37520</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>1860</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+      <c r="G7">
+        <v>221</v>
+      </c>
+      <c r="H7">
+        <v>1920</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>2820</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>33</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1980</v>
+      </c>
+      <c r="I9">
+        <v>37500</v>
+      </c>
+      <c r="J9">
+        <v>39480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>221</v>
+      </c>
+      <c r="H10">
+        <v>1800</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>33</v>
+      </c>
+      <c r="D11">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>117</v>
+      </c>
+      <c r="H11">
+        <v>2460</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>39</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2340</v>
+      </c>
+      <c r="I12">
+        <v>10000</v>
+      </c>
+      <c r="J12">
+        <v>12340</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
+      </c>
+      <c r="D13">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>91</v>
+      </c>
+      <c r="H13">
+        <v>2040</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>39</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>156</v>
+      </c>
+      <c r="H14">
+        <v>2040</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>260</v>
+      </c>
+      <c r="H15">
+        <v>1560</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>130</v>
+      </c>
+      <c r="H16">
+        <v>2640</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2770</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>52</v>
+      </c>
+      <c r="H17">
+        <v>1920</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>48</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>2880</v>
+      </c>
+      <c r="I18">
+        <v>5000</v>
+      </c>
+      <c r="J18">
+        <v>7880</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>32</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1920</v>
+      </c>
+      <c r="I19">
+        <v>30000</v>
+      </c>
+      <c r="J19">
+        <v>31920</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>48</v>
+      </c>
+      <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2820</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>32</v>
+      </c>
+      <c r="D21">
+        <v>33</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1980</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <v>104</v>
+      </c>
+      <c r="H22">
+        <v>2340</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>41</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>2460</v>
+      </c>
+      <c r="I23">
+        <v>5000</v>
+      </c>
+      <c r="J23">
+        <v>7460</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>91</v>
+      </c>
+      <c r="H24">
+        <v>1920</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>41</v>
+      </c>
+      <c r="D25">
+        <v>48</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>2880</v>
+      </c>
+      <c r="I25">
+        <v>7500</v>
+      </c>
+      <c r="J25">
+        <v>10380</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>32</v>
+      </c>
+      <c r="E26">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>1920</v>
+      </c>
+      <c r="I26">
+        <v>27500</v>
+      </c>
+      <c r="J26">
+        <v>29420</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27">
+        <v>42</v>
+      </c>
+      <c r="C27">
+        <v>48</v>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>6</v>
+      </c>
+      <c r="G27">
+        <v>78</v>
+      </c>
+      <c r="H27">
+        <v>2520</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>32</v>
+      </c>
+      <c r="D28">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>7</v>
+      </c>
+      <c r="G28">
+        <v>91</v>
+      </c>
+      <c r="H28">
+        <v>1860</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>273</v>
+      </c>
+      <c r="H29">
+        <v>1680</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>28</v>
+      </c>
+      <c r="G30">
+        <v>364</v>
+      </c>
+      <c r="H30">
+        <v>1440</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>28</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
       <c r="E31">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>176</v>
+        <v>26</v>
       </c>
       <c r="G31">
-        <v>2288</v>
+        <v>338</v>
       </c>
       <c r="H31">
         <v>1800</v>
@@ -2998,1095 +5270,3293 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>4088</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" t="s">
-        <v>87</v>
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>51</v>
       </c>
       <c r="C32">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D32">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>2288</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J32">
-        <v>4088</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" t="s">
-        <v>88</v>
+        <v>62</v>
+      </c>
+      <c r="B33">
+        <v>40</v>
       </c>
       <c r="C33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>1800</v>
+      </c>
+      <c r="I33">
+        <v>25000</v>
+      </c>
+      <c r="J33">
+        <v>26800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>78</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>546</v>
+      </c>
+      <c r="H2">
+        <v>4680</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>5226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2520</v>
+      </c>
+      <c r="I3">
+        <v>5000</v>
+      </c>
+      <c r="J3">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>78</v>
+      </c>
+      <c r="D4">
+        <v>39</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>39</v>
+      </c>
+      <c r="G4">
+        <v>507</v>
+      </c>
+      <c r="H4">
+        <v>2340</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>325</v>
+      </c>
+      <c r="H5">
+        <v>3360</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>429</v>
+      </c>
+      <c r="H6">
+        <v>1860</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>57</v>
+      </c>
+      <c r="G7">
+        <v>741</v>
+      </c>
+      <c r="H7">
+        <v>1920</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>533</v>
+      </c>
+      <c r="H8">
+        <v>2820</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>325</v>
+      </c>
+      <c r="H9">
+        <v>2880</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>546</v>
+      </c>
+      <c r="H10">
+        <v>1800</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>48</v>
+      </c>
+      <c r="D11">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>49</v>
+      </c>
+      <c r="G11">
+        <v>637</v>
+      </c>
+      <c r="H11">
+        <v>2460</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3097</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>36</v>
+      </c>
+      <c r="G12">
+        <v>468</v>
+      </c>
+      <c r="H12">
+        <v>2580</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3048</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
+      </c>
+      <c r="D13">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>43</v>
+      </c>
+      <c r="G13">
+        <v>559</v>
+      </c>
+      <c r="H13">
+        <v>2040</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>676</v>
+      </c>
+      <c r="H14">
+        <v>2040</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2716</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>780</v>
+      </c>
+      <c r="H15">
+        <v>1560</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16">
+        <v>650</v>
+      </c>
+      <c r="H16">
+        <v>2640</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>44</v>
+      </c>
+      <c r="G17">
+        <v>572</v>
+      </c>
+      <c r="H17">
+        <v>1920</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>38</v>
+      </c>
+      <c r="G18">
+        <v>494</v>
+      </c>
+      <c r="H18">
+        <v>3000</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>3494</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>26</v>
+      </c>
+      <c r="G19">
+        <v>338</v>
+      </c>
+      <c r="H19">
+        <v>2640</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2978</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>29</v>
+      </c>
+      <c r="G20">
+        <v>377</v>
+      </c>
+      <c r="H20">
+        <v>2820</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>33</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>520</v>
+      </c>
+      <c r="H21">
+        <v>1980</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>48</v>
+      </c>
+      <c r="G22">
+        <v>624</v>
+      </c>
+      <c r="H22">
+        <v>2340</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>38</v>
+      </c>
+      <c r="G23">
+        <v>494</v>
+      </c>
+      <c r="H23">
+        <v>2580</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>45</v>
+      </c>
+      <c r="G24">
+        <v>585</v>
+      </c>
+      <c r="H24">
+        <v>1920</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>51</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>37</v>
+      </c>
+      <c r="G25">
+        <v>481</v>
+      </c>
+      <c r="H25">
+        <v>3060</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>3541</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>43</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>26</v>
+      </c>
+      <c r="G26">
+        <v>338</v>
+      </c>
+      <c r="H26">
+        <v>2580</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2918</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27">
+        <v>42</v>
+      </c>
+      <c r="C27">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>35</v>
+      </c>
+      <c r="G27">
+        <v>455</v>
+      </c>
+      <c r="H27">
+        <v>2520</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>43</v>
+      </c>
+      <c r="D28">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>47</v>
+      </c>
+      <c r="G28">
+        <v>611</v>
+      </c>
+      <c r="H28">
+        <v>1860</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>61</v>
+      </c>
+      <c r="G29">
+        <v>793</v>
+      </c>
+      <c r="H29">
+        <v>1680</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>68</v>
+      </c>
+      <c r="G30">
+        <v>884</v>
+      </c>
+      <c r="H30">
+        <v>1440</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>28</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>66</v>
+      </c>
+      <c r="G31">
+        <v>858</v>
+      </c>
+      <c r="H31">
+        <v>1800</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>51</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>39</v>
+      </c>
+      <c r="G32">
+        <v>507</v>
+      </c>
+      <c r="H32">
+        <v>3060</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33">
+        <v>40</v>
+      </c>
+      <c r="C33">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
       <c r="F33">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="G33">
-        <v>2301</v>
+        <v>377</v>
       </c>
       <c r="H33">
-        <v>2160</v>
+        <v>2400</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>4461</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>118</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>546</v>
+      </c>
+      <c r="H2">
+        <v>7080</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>7626</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2520</v>
+      </c>
+      <c r="I3">
+        <v>5000</v>
+      </c>
+      <c r="J3">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>118</v>
+      </c>
+      <c r="D4">
+        <v>39</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>79</v>
+      </c>
+      <c r="G4">
+        <v>1027</v>
+      </c>
+      <c r="H4">
+        <v>2340</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>65</v>
+      </c>
+      <c r="G5">
+        <v>845</v>
+      </c>
+      <c r="H5">
+        <v>3360</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>73</v>
+      </c>
+      <c r="G6">
+        <v>949</v>
+      </c>
+      <c r="H6">
+        <v>1860</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>97</v>
+      </c>
+      <c r="G7">
+        <v>1261</v>
+      </c>
+      <c r="H7">
+        <v>1920</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8">
+        <v>1053</v>
+      </c>
+      <c r="H8">
+        <v>2820</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>65</v>
+      </c>
+      <c r="G9">
+        <v>845</v>
+      </c>
+      <c r="H9">
+        <v>2880</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>82</v>
+      </c>
+      <c r="G10">
+        <v>1066</v>
+      </c>
+      <c r="H10">
+        <v>1800</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>48</v>
+      </c>
+      <c r="D11">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>89</v>
       </c>
-      <c r="C34">
+      <c r="G11">
+        <v>1157</v>
+      </c>
+      <c r="H11">
+        <v>2460</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>76</v>
+      </c>
+      <c r="G12">
+        <v>988</v>
+      </c>
+      <c r="H12">
+        <v>2580</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>3568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
+      </c>
+      <c r="D13">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>83</v>
+      </c>
+      <c r="G13">
+        <v>1079</v>
+      </c>
+      <c r="H13">
+        <v>2040</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>92</v>
+      </c>
+      <c r="G14">
+        <v>1196</v>
+      </c>
+      <c r="H14">
+        <v>2040</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>100</v>
+      </c>
+      <c r="G15">
+        <v>1300</v>
+      </c>
+      <c r="H15">
+        <v>1560</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>90</v>
+      </c>
+      <c r="G16">
+        <v>1170</v>
+      </c>
+      <c r="H16">
+        <v>2640</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>84</v>
+      </c>
+      <c r="G17">
+        <v>1092</v>
+      </c>
+      <c r="H17">
+        <v>1920</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>78</v>
+      </c>
+      <c r="G18">
+        <v>1014</v>
+      </c>
+      <c r="H18">
+        <v>3000</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>66</v>
+      </c>
+      <c r="G19">
+        <v>858</v>
+      </c>
+      <c r="H19">
+        <v>2640</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>3498</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>69</v>
+      </c>
+      <c r="G20">
+        <v>897</v>
+      </c>
+      <c r="H20">
+        <v>2820</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>33</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>1040</v>
+      </c>
+      <c r="H21">
+        <v>1980</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>88</v>
+      </c>
+      <c r="G22">
+        <v>1144</v>
+      </c>
+      <c r="H22">
+        <v>2340</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>3484</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>78</v>
+      </c>
+      <c r="G23">
+        <v>1014</v>
+      </c>
+      <c r="H23">
+        <v>2580</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>85</v>
+      </c>
+      <c r="G24">
+        <v>1105</v>
+      </c>
+      <c r="H24">
+        <v>1920</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>51</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>77</v>
+      </c>
+      <c r="G25">
+        <v>1001</v>
+      </c>
+      <c r="H25">
+        <v>3060</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>43</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>66</v>
+      </c>
+      <c r="G26">
+        <v>858</v>
+      </c>
+      <c r="H26">
+        <v>2580</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27">
+        <v>42</v>
+      </c>
+      <c r="C27">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>75</v>
+      </c>
+      <c r="G27">
+        <v>975</v>
+      </c>
+      <c r="H27">
+        <v>2520</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>43</v>
+      </c>
+      <c r="D28">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>87</v>
+      </c>
+      <c r="G28">
+        <v>1131</v>
+      </c>
+      <c r="H28">
+        <v>1860</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>101</v>
+      </c>
+      <c r="G29">
+        <v>1313</v>
+      </c>
+      <c r="H29">
+        <v>1680</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2993</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>108</v>
+      </c>
+      <c r="G30">
+        <v>1404</v>
+      </c>
+      <c r="H30">
+        <v>1440</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>28</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>106</v>
+      </c>
+      <c r="G31">
+        <v>1378</v>
+      </c>
+      <c r="H31">
+        <v>1800</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>51</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>79</v>
+      </c>
+      <c r="G32">
+        <v>1027</v>
+      </c>
+      <c r="H32">
+        <v>3060</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33">
+        <v>40</v>
+      </c>
+      <c r="C33">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>69</v>
+      </c>
+      <c r="G33">
+        <v>897</v>
+      </c>
+      <c r="H33">
+        <v>2400</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="D34">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
-      <c r="E34">
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>158</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>546</v>
+      </c>
+      <c r="H2">
+        <v>9480</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>10026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2520</v>
+      </c>
+      <c r="I3">
+        <v>5000</v>
+      </c>
+      <c r="J3">
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>158</v>
+      </c>
+      <c r="D4">
+        <v>39</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>119</v>
+      </c>
+      <c r="G4">
+        <v>1547</v>
+      </c>
+      <c r="H4">
+        <v>2340</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>42</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>105</v>
+      </c>
+      <c r="G5">
+        <v>1365</v>
+      </c>
+      <c r="H5">
+        <v>3360</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>39</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>113</v>
+      </c>
+      <c r="G6">
+        <v>1469</v>
+      </c>
+      <c r="H6">
+        <v>1860</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>137</v>
+      </c>
+      <c r="G7">
+        <v>1781</v>
+      </c>
+      <c r="H7">
+        <v>1920</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>47</v>
+      </c>
+      <c r="C8">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>47</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>121</v>
+      </c>
+      <c r="G8">
+        <v>1573</v>
+      </c>
+      <c r="H8">
+        <v>2820</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>105</v>
+      </c>
+      <c r="G9">
+        <v>1365</v>
+      </c>
+      <c r="H9">
+        <v>2880</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>47</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>122</v>
+      </c>
+      <c r="G10">
+        <v>1586</v>
+      </c>
+      <c r="H10">
+        <v>1800</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11">
         <v>41</v>
       </c>
-      <c r="F34">
-        <v>178</v>
-      </c>
-      <c r="G34">
-        <v>2314</v>
-      </c>
-      <c r="H34">
+      <c r="C11">
+        <v>48</v>
+      </c>
+      <c r="D11">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>129</v>
+      </c>
+      <c r="G11">
+        <v>1677</v>
+      </c>
+      <c r="H11">
         <v>2460</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>4774</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C35">
-        <v>29</v>
-      </c>
-      <c r="D35">
-        <v>36</v>
-      </c>
-      <c r="E35">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12">
         <v>43</v>
       </c>
-      <c r="F35">
-        <v>185</v>
-      </c>
-      <c r="G35">
-        <v>2405</v>
-      </c>
-      <c r="H35">
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>116</v>
+      </c>
+      <c r="G12">
+        <v>1508</v>
+      </c>
+      <c r="H12">
         <v>2580</v>
       </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>4985</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>41</v>
+      </c>
+      <c r="D13">
+        <v>34</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>123</v>
+      </c>
+      <c r="G13">
+        <v>1599</v>
+      </c>
+      <c r="H13">
+        <v>2040</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>43</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>132</v>
+      </c>
+      <c r="G14">
+        <v>1716</v>
+      </c>
+      <c r="H14">
+        <v>2040</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>3756</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>26</v>
+      </c>
+      <c r="C15">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>140</v>
+      </c>
+      <c r="G15">
+        <v>1820</v>
+      </c>
+      <c r="H15">
+        <v>1560</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>3380</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>130</v>
+      </c>
+      <c r="G16">
+        <v>1690</v>
+      </c>
+      <c r="H16">
+        <v>2640</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>26</v>
+      </c>
+      <c r="D17">
+        <v>32</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>124</v>
+      </c>
+      <c r="G17">
+        <v>1612</v>
+      </c>
+      <c r="H17">
+        <v>1920</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>3532</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <v>44</v>
+      </c>
+      <c r="D18">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>118</v>
+      </c>
+      <c r="G18">
+        <v>1534</v>
+      </c>
+      <c r="H18">
+        <v>3000</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
+      </c>
+      <c r="D19">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>106</v>
+      </c>
+      <c r="G19">
+        <v>1378</v>
+      </c>
+      <c r="H19">
+        <v>2640</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>109</v>
+      </c>
+      <c r="G20">
+        <v>1417</v>
+      </c>
+      <c r="H20">
+        <v>2820</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>4237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>44</v>
+      </c>
+      <c r="D21">
+        <v>33</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>120</v>
+      </c>
+      <c r="G21">
+        <v>1560</v>
+      </c>
+      <c r="H21">
+        <v>1980</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>3540</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22">
+        <v>39</v>
+      </c>
+      <c r="C22">
+        <v>47</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>128</v>
+      </c>
+      <c r="G22">
+        <v>1664</v>
+      </c>
+      <c r="H22">
+        <v>2340</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>33</v>
+      </c>
+      <c r="D23">
+        <v>43</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>118</v>
+      </c>
+      <c r="G23">
+        <v>1534</v>
+      </c>
+      <c r="H23">
+        <v>2580</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24">
+        <v>32</v>
+      </c>
+      <c r="C24">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>32</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>125</v>
+      </c>
+      <c r="G24">
+        <v>1625</v>
+      </c>
+      <c r="H24">
+        <v>1920</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>3545</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>43</v>
+      </c>
+      <c r="D25">
+        <v>51</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>117</v>
+      </c>
+      <c r="G25">
+        <v>1521</v>
+      </c>
+      <c r="H25">
+        <v>3060</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4581</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>43</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>106</v>
+      </c>
+      <c r="G26">
+        <v>1378</v>
+      </c>
+      <c r="H26">
+        <v>2580</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27">
+        <v>42</v>
+      </c>
+      <c r="C27">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>42</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>115</v>
+      </c>
+      <c r="G27">
+        <v>1495</v>
+      </c>
+      <c r="H27">
+        <v>2520</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>43</v>
+      </c>
+      <c r="D28">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>127</v>
+      </c>
+      <c r="G28">
+        <v>1651</v>
+      </c>
+      <c r="H28">
+        <v>1860</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>3511</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>141</v>
+      </c>
+      <c r="G29">
+        <v>1833</v>
+      </c>
+      <c r="H29">
+        <v>1680</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>3513</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30">
+        <v>24</v>
+      </c>
+      <c r="C30">
+        <v>31</v>
+      </c>
+      <c r="D30">
+        <v>24</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>148</v>
+      </c>
+      <c r="G30">
+        <v>1924</v>
+      </c>
+      <c r="H30">
+        <v>1440</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>28</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>146</v>
+      </c>
+      <c r="G31">
+        <v>1898</v>
+      </c>
+      <c r="H31">
+        <v>1800</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32">
+        <v>51</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>119</v>
+      </c>
+      <c r="G32">
+        <v>1547</v>
+      </c>
+      <c r="H32">
+        <v>3060</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4607</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33">
         <v>40</v>
       </c>
-      <c r="D36">
-        <v>41</v>
-      </c>
-      <c r="E36">
-        <v>41</v>
-      </c>
-      <c r="F36">
-        <v>186</v>
-      </c>
-      <c r="G36">
-        <v>2418</v>
-      </c>
-      <c r="H36">
-        <v>2460</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>4878</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>94</v>
-      </c>
-      <c r="B37" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37">
+      <c r="C33">
+        <v>30</v>
+      </c>
+      <c r="D33">
         <v>40</v>
       </c>
-      <c r="D37">
-        <v>43</v>
-      </c>
-      <c r="E37">
-        <v>37</v>
-      </c>
-      <c r="F37">
-        <v>189</v>
-      </c>
-      <c r="G37">
-        <v>2457</v>
-      </c>
-      <c r="H37">
-        <v>2220</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>4677</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38">
-        <v>40</v>
-      </c>
-      <c r="D38">
-        <v>41</v>
-      </c>
-      <c r="E38">
-        <v>35</v>
-      </c>
-      <c r="F38">
-        <v>190</v>
-      </c>
-      <c r="G38">
-        <v>2470</v>
-      </c>
-      <c r="H38">
-        <v>2100</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>4570</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39">
-        <v>40</v>
-      </c>
-      <c r="D39">
-        <v>37</v>
-      </c>
-      <c r="E39">
-        <v>36</v>
-      </c>
-      <c r="F39">
-        <v>187</v>
-      </c>
-      <c r="G39">
-        <v>2431</v>
-      </c>
-      <c r="H39">
-        <v>2160</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>4591</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40">
-        <v>37</v>
-      </c>
-      <c r="D40">
-        <v>35</v>
-      </c>
-      <c r="E40">
-        <v>36</v>
-      </c>
-      <c r="F40">
-        <v>185</v>
-      </c>
-      <c r="G40">
-        <v>2405</v>
-      </c>
-      <c r="H40">
-        <v>2160</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>4565</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41">
-        <v>36</v>
-      </c>
-      <c r="D41">
-        <v>36</v>
-      </c>
-      <c r="E41">
-        <v>37</v>
-      </c>
-      <c r="F41">
-        <v>185</v>
-      </c>
-      <c r="G41">
-        <v>2405</v>
-      </c>
-      <c r="H41">
-        <v>2220</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>4625</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42" t="s">
-        <v>97</v>
-      </c>
-      <c r="C42">
-        <v>36</v>
-      </c>
-      <c r="D42">
-        <v>36</v>
-      </c>
-      <c r="E42">
-        <v>38</v>
-      </c>
-      <c r="F42">
-        <v>185</v>
-      </c>
-      <c r="G42">
-        <v>2405</v>
-      </c>
-      <c r="H42">
-        <v>2280</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>4685</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43">
-        <v>36</v>
-      </c>
-      <c r="D43">
-        <v>37</v>
-      </c>
-      <c r="E43">
-        <v>35</v>
-      </c>
-      <c r="F43">
-        <v>186</v>
-      </c>
-      <c r="G43">
-        <v>2418</v>
-      </c>
-      <c r="H43">
-        <v>2100</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
-        <v>4518</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44">
-        <v>37</v>
-      </c>
-      <c r="D44">
-        <v>38</v>
-      </c>
-      <c r="E44">
-        <v>36</v>
-      </c>
-      <c r="F44">
-        <v>187</v>
-      </c>
-      <c r="G44">
-        <v>2431</v>
-      </c>
-      <c r="H44">
-        <v>2160</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>4591</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45">
-        <v>39</v>
-      </c>
-      <c r="D45">
-        <v>35</v>
-      </c>
-      <c r="E45">
-        <v>38</v>
-      </c>
-      <c r="F45">
-        <v>183</v>
-      </c>
-      <c r="G45">
-        <v>2379</v>
-      </c>
-      <c r="H45">
-        <v>2280</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>4659</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>103</v>
-      </c>
-      <c r="B46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46">
-        <v>32</v>
-      </c>
-      <c r="D46">
-        <v>36</v>
-      </c>
-      <c r="E46">
-        <v>44</v>
-      </c>
-      <c r="F46">
-        <v>187</v>
-      </c>
-      <c r="G46">
-        <v>2431</v>
-      </c>
-      <c r="H46">
-        <v>2640</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>5071</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B47" t="s">
-        <v>102</v>
-      </c>
-      <c r="C47">
-        <v>39</v>
-      </c>
-      <c r="D47">
-        <v>38</v>
-      </c>
-      <c r="E47">
-        <v>47</v>
-      </c>
-      <c r="F47">
-        <v>186</v>
-      </c>
-      <c r="G47">
-        <v>2418</v>
-      </c>
-      <c r="H47">
-        <v>2820</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>5238</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48">
-        <v>39</v>
-      </c>
-      <c r="D48">
-        <v>44</v>
-      </c>
-      <c r="E48">
-        <v>46</v>
-      </c>
-      <c r="F48">
-        <v>191</v>
-      </c>
-      <c r="G48">
-        <v>2483</v>
-      </c>
-      <c r="H48">
-        <v>2760</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>5243</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B49" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49">
-        <v>45</v>
-      </c>
-      <c r="D49">
-        <v>47</v>
-      </c>
-      <c r="E49">
-        <v>45</v>
-      </c>
-      <c r="F49">
-        <v>193</v>
-      </c>
-      <c r="G49">
-        <v>2509</v>
-      </c>
-      <c r="H49">
-        <v>2700</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>5209</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>107</v>
-      </c>
-      <c r="B50" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50">
-        <v>45</v>
-      </c>
-      <c r="D50">
-        <v>46</v>
-      </c>
-      <c r="E50">
-        <v>37</v>
-      </c>
-      <c r="F50">
-        <v>194</v>
-      </c>
-      <c r="G50">
-        <v>2522</v>
-      </c>
-      <c r="H50">
-        <v>2220</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>4742</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>108</v>
-      </c>
-      <c r="B51" t="s">
-        <v>106</v>
-      </c>
-      <c r="C51">
-        <v>45</v>
-      </c>
-      <c r="D51">
-        <v>45</v>
-      </c>
-      <c r="E51">
-        <v>26</v>
-      </c>
-      <c r="F51">
-        <v>194</v>
-      </c>
-      <c r="G51">
-        <v>2522</v>
-      </c>
-      <c r="H51">
-        <v>1560</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>4082</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
         <v>109</v>
       </c>
-      <c r="B52" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52">
-        <v>45</v>
-      </c>
-      <c r="D52">
-        <v>37</v>
-      </c>
-      <c r="E52">
-        <v>21</v>
-      </c>
-      <c r="F52">
-        <v>186</v>
-      </c>
-      <c r="G52">
-        <v>2418</v>
-      </c>
-      <c r="H52">
-        <v>1260</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>3678</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>110</v>
-      </c>
-      <c r="B53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53">
-        <v>33</v>
-      </c>
-      <c r="D53">
-        <v>26</v>
-      </c>
-      <c r="E53">
-        <v>21</v>
-      </c>
-      <c r="F53">
-        <v>179</v>
-      </c>
-      <c r="G53">
-        <v>2327</v>
-      </c>
-      <c r="H53">
-        <v>1260</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-      <c r="J53">
-        <v>3587</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>111</v>
-      </c>
-      <c r="B54" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54">
-        <v>24</v>
-      </c>
-      <c r="D54">
-        <v>21</v>
-      </c>
-      <c r="E54">
-        <v>23</v>
-      </c>
-      <c r="F54">
-        <v>176</v>
-      </c>
-      <c r="G54">
-        <v>2288</v>
-      </c>
-      <c r="H54">
-        <v>1380</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-      <c r="J54">
-        <v>3668</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" t="s">
-        <v>110</v>
-      </c>
-      <c r="C55">
-        <v>24</v>
-      </c>
-      <c r="D55">
-        <v>21</v>
-      </c>
-      <c r="E55">
-        <v>42</v>
-      </c>
-      <c r="F55">
-        <v>173</v>
-      </c>
-      <c r="G55">
-        <v>2249</v>
-      </c>
-      <c r="H55">
-        <v>2520</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>4769</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B56" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56">
-        <v>24</v>
-      </c>
-      <c r="D56">
-        <v>23</v>
-      </c>
-      <c r="E56">
-        <v>54</v>
-      </c>
-      <c r="F56">
-        <v>172</v>
-      </c>
-      <c r="G56">
-        <v>2236</v>
-      </c>
-      <c r="H56">
-        <v>3240</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>5476</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>114</v>
-      </c>
-      <c r="B57" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57">
-        <v>24</v>
-      </c>
-      <c r="D57">
-        <v>42</v>
-      </c>
-      <c r="E57">
-        <v>55</v>
-      </c>
-      <c r="F57">
-        <v>190</v>
-      </c>
-      <c r="G57">
-        <v>2470</v>
-      </c>
-      <c r="H57">
-        <v>3300</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>5770</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58">
-        <v>50</v>
-      </c>
-      <c r="D58">
-        <v>54</v>
-      </c>
-      <c r="E58">
-        <v>51</v>
-      </c>
-      <c r="F58">
-        <v>194</v>
-      </c>
-      <c r="G58">
-        <v>2522</v>
-      </c>
-      <c r="H58">
-        <v>3060</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>5582</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59">
-        <v>50</v>
-      </c>
-      <c r="D59">
-        <v>55</v>
-      </c>
-      <c r="E59">
-        <v>45</v>
-      </c>
-      <c r="F59">
-        <v>199</v>
-      </c>
-      <c r="G59">
-        <v>2587</v>
-      </c>
-      <c r="H59">
-        <v>2700</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>5287</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60">
-        <v>50</v>
-      </c>
-      <c r="D60">
-        <v>51</v>
-      </c>
-      <c r="E60">
-        <v>32</v>
-      </c>
-      <c r="F60">
-        <v>200</v>
-      </c>
-      <c r="G60">
-        <v>2600</v>
-      </c>
-      <c r="H60">
-        <v>1920</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>4520</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>118</v>
-      </c>
-      <c r="B61" t="s">
-        <v>116</v>
-      </c>
-      <c r="C61">
-        <v>50</v>
-      </c>
-      <c r="D61">
-        <v>45</v>
-      </c>
-      <c r="E61">
-        <v>36</v>
-      </c>
-      <c r="F61">
-        <v>195</v>
-      </c>
-      <c r="G61">
-        <v>2535</v>
-      </c>
-      <c r="H61">
-        <v>2160</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>4695</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62">
-        <v>44</v>
-      </c>
-      <c r="D62">
-        <v>32</v>
-      </c>
-      <c r="E62">
-        <v>37</v>
-      </c>
-      <c r="F62">
-        <v>183</v>
-      </c>
-      <c r="G62">
-        <v>2379</v>
-      </c>
-      <c r="H62">
-        <v>2220</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>4599</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>120</v>
-      </c>
-      <c r="B63" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63">
-        <v>27</v>
-      </c>
-      <c r="D63">
-        <v>36</v>
-      </c>
-      <c r="E63">
-        <v>38</v>
-      </c>
-      <c r="F63">
-        <v>192</v>
-      </c>
-      <c r="G63">
-        <v>2496</v>
-      </c>
-      <c r="H63">
-        <v>2280</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>4776</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>121</v>
-      </c>
-      <c r="B64" t="s">
-        <v>119</v>
-      </c>
-      <c r="C64">
-        <v>45</v>
-      </c>
-      <c r="D64">
-        <v>37</v>
-      </c>
-      <c r="E64">
-        <v>36</v>
-      </c>
-      <c r="F64">
-        <v>184</v>
-      </c>
-      <c r="G64">
-        <v>2392</v>
-      </c>
-      <c r="H64">
-        <v>2160</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>4552</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>122</v>
-      </c>
-      <c r="B65" t="s">
-        <v>120</v>
-      </c>
-      <c r="C65">
-        <v>36</v>
-      </c>
-      <c r="D65">
-        <v>38</v>
-      </c>
-      <c r="E65">
-        <v>35</v>
-      </c>
-      <c r="F65">
-        <v>186</v>
-      </c>
-      <c r="G65">
-        <v>2418</v>
-      </c>
-      <c r="H65">
-        <v>2100</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>4518</v>
+      <c r="G33">
+        <v>1417</v>
+      </c>
+      <c r="H33">
+        <v>2400</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>3817</v>
       </c>
     </row>
   </sheetData>
